--- a/design_issues/sonarqube/P4_JobApplication.xlsx
+++ b/design_issues/sonarqube/P4_JobApplication.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="194">
   <si>
     <t>severity</t>
   </si>
@@ -244,9 +244,6 @@
     <t>'category._id' is missing in props validation</t>
   </si>
   <si>
-    <t>Ambiguous spacing after previous element input</t>
-  </si>
-  <si>
     <t>A form label must be associated with a control.</t>
   </si>
   <si>
@@ -350,12 +347,6 @@
   </si>
   <si>
     <t>src/components/jobs/JobListing.js</t>
-  </si>
-  <si>
-    <t>src/components/pages/LandingPage.js</t>
-  </si>
-  <si>
-    <t>Ambiguous spacing before next element span</t>
   </si>
   <si>
     <t>src/components/profile/Profile.js</t>
@@ -553,6 +544,12 @@
     <t>Unexpected duplicate selector "...", first used at line ...</t>
   </si>
   <si>
+    <t>Prefer explicit Number methods instead of global functions.</t>
+  </si>
+  <si>
+    <t>...' is missing in props validation</t>
+  </si>
+  <si>
     <t>HTML entity, ... , must be escaped.</t>
   </si>
   <si>
@@ -565,18 +562,30 @@
     <t>The signature '...' of '...' is deprecated.</t>
   </si>
   <si>
+    <t>Use the node: protocol for Node.js core module imports.</t>
+  </si>
+  <si>
     <t>Prefer String#replaceAll() over String#replace().</t>
   </si>
   <si>
     <t>Use for…of instead of .forEach(...).</t>
   </si>
   <si>
+    <t>onMouseOver/onMouseOut must be accompanied by onFocus/onBlur for accessibility.</t>
+  </si>
+  <si>
     <t>Remove this useless assignment to variable "...".</t>
   </si>
   <si>
     <t>Remove the declaration of the unused '...' variable.</t>
   </si>
   <si>
+    <t>Ensure proper Promise handling and type consistency.</t>
+  </si>
+  <si>
+    <t>Use modern string methods instead of deprecated substr().</t>
+  </si>
+  <si>
     <t>Remove this use of the output from "..."; "..." doesn't return anything.</t>
   </si>
   <si>
@@ -586,52 +595,32 @@
     <t>Duplicate name '...'.</t>
   </si>
   <si>
+    <t>Avoid unreliable instanceof checks for type safety.</t>
+  </si>
+  <si>
     <t>This condition is covered by the one on line ...</t>
   </si>
   <si>
-    <t>...' is missing in props validation</t>
-  </si>
-  <si>
-    <t>Use the node: protocol for Node.js core module imports.</t>
-  </si>
-  <si>
-    <t>Prefer explicit Number methods instead of global functions.</t>
+    <t>Create interactive elements with full accessibility.</t>
   </si>
   <si>
     <t>Remove this unused import of '...'</t>
   </si>
   <si>
-    <t>Create interactive elements with full accessibility.</t>
-  </si>
-  <si>
-    <t>Use modern string methods instead of deprecated substr().</t>
-  </si>
-  <si>
-    <t>Ensure proper Promise handling and type consistency.</t>
-  </si>
-  <si>
-    <t>onMouseOver/onMouseOut must be accompanied by onFocus/onBlur for accessibility.</t>
-  </si>
-  <si>
-    <t>Avoid unreliable instanceof checks for type safety.</t>
+    <t>...' is deprecated.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -660,16 +649,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -677,15 +666,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -988,13 +972,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="119.54296875" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="2" max="2" width="33.26953125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="47.453125" customWidth="1"/>
+    <col min="6" max="6" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -3285,7 +3269,7 @@
         <v>52</v>
       </c>
       <c r="D100">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E100" t="s">
         <v>74</v>
@@ -3308,13 +3292,13 @@
         <v>52</v>
       </c>
       <c r="D101">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E101" t="s">
         <v>75</v>
       </c>
       <c r="F101" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G101" t="s">
         <v>19</v>
@@ -3331,13 +3315,13 @@
         <v>52</v>
       </c>
       <c r="D102">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E102" t="s">
         <v>76</v>
       </c>
       <c r="F102" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G102" t="s">
         <v>19</v>
@@ -3354,10 +3338,10 @@
         <v>52</v>
       </c>
       <c r="D103">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="E103" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -3377,13 +3361,13 @@
         <v>52</v>
       </c>
       <c r="D104">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E104" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G104" t="s">
         <v>19</v>
@@ -3400,13 +3384,13 @@
         <v>52</v>
       </c>
       <c r="D105">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="E105" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F105" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G105" t="s">
         <v>19</v>
@@ -3423,10 +3407,10 @@
         <v>52</v>
       </c>
       <c r="D106">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="E106" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
@@ -3437,25 +3421,25 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C107" t="s">
         <v>52</v>
       </c>
       <c r="D107">
-        <v>423</v>
+        <v>38</v>
       </c>
       <c r="E107" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
       </c>
       <c r="G107" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -3463,16 +3447,16 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
+        <v>80</v>
+      </c>
+      <c r="C108" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108">
+        <v>52</v>
+      </c>
+      <c r="E108" t="s">
         <v>79</v>
-      </c>
-      <c r="C108" t="s">
-        <v>52</v>
-      </c>
-      <c r="D108">
-        <v>38</v>
-      </c>
-      <c r="E108" t="s">
-        <v>80</v>
       </c>
       <c r="F108" t="s">
         <v>11</v>
@@ -3483,25 +3467,25 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B109" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C109" t="s">
         <v>52</v>
       </c>
       <c r="D109">
-        <v>52</v>
+        <v>194</v>
       </c>
       <c r="E109" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F109" t="s">
         <v>11</v>
       </c>
       <c r="G109" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
@@ -3509,16 +3493,16 @@
         <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C110" t="s">
         <v>52</v>
       </c>
       <c r="D110">
-        <v>194</v>
+        <v>271</v>
       </c>
       <c r="E110" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F110" t="s">
         <v>11</v>
@@ -3532,13 +3516,13 @@
         <v>33</v>
       </c>
       <c r="B111" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C111" t="s">
         <v>52</v>
       </c>
       <c r="D111">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E111" t="s">
         <v>50</v>
@@ -3555,16 +3539,16 @@
         <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C112" t="s">
         <v>52</v>
       </c>
       <c r="D112">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E112" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -3575,22 +3559,22 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B113" t="s">
+        <v>80</v>
+      </c>
+      <c r="C113" t="s">
+        <v>52</v>
+      </c>
+      <c r="D113">
+        <v>321</v>
+      </c>
+      <c r="E113" t="s">
         <v>81</v>
       </c>
-      <c r="C113" t="s">
-        <v>52</v>
-      </c>
-      <c r="D113">
-        <v>284</v>
-      </c>
-      <c r="E113" t="s">
-        <v>53</v>
-      </c>
       <c r="F113" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G113" t="s">
         <v>19</v>
@@ -3601,13 +3585,13 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C114" t="s">
         <v>52</v>
       </c>
       <c r="D114">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E114" t="s">
         <v>82</v>
@@ -3624,16 +3608,16 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
+        <v>80</v>
+      </c>
+      <c r="C115" t="s">
+        <v>52</v>
+      </c>
+      <c r="D115">
+        <v>340</v>
+      </c>
+      <c r="E115" t="s">
         <v>81</v>
-      </c>
-      <c r="C115" t="s">
-        <v>52</v>
-      </c>
-      <c r="D115">
-        <v>322</v>
-      </c>
-      <c r="E115" t="s">
-        <v>83</v>
       </c>
       <c r="F115" t="s">
         <v>40</v>
@@ -3647,13 +3631,13 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C116" t="s">
         <v>52</v>
       </c>
       <c r="D116">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E116" t="s">
         <v>82</v>
@@ -3667,22 +3651,22 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C117" t="s">
         <v>52</v>
       </c>
       <c r="D117">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="E117" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="F117" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G117" t="s">
         <v>19</v>
@@ -3690,22 +3674,22 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B118" t="s">
+        <v>80</v>
+      </c>
+      <c r="C118" t="s">
+        <v>52</v>
+      </c>
+      <c r="D118">
+        <v>444</v>
+      </c>
+      <c r="E118" t="s">
         <v>81</v>
       </c>
-      <c r="C118" t="s">
-        <v>52</v>
-      </c>
-      <c r="D118">
-        <v>388</v>
-      </c>
-      <c r="E118" t="s">
-        <v>54</v>
-      </c>
       <c r="F118" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G118" t="s">
         <v>19</v>
@@ -3716,13 +3700,13 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C119" t="s">
         <v>52</v>
       </c>
       <c r="D119">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E119" t="s">
         <v>82</v>
@@ -3736,22 +3720,22 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B120" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C120" t="s">
         <v>52</v>
       </c>
       <c r="D120">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E120" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F120" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G120" t="s">
         <v>19</v>
@@ -3759,22 +3743,22 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B121" t="s">
+        <v>80</v>
+      </c>
+      <c r="C121" t="s">
+        <v>52</v>
+      </c>
+      <c r="D121">
+        <v>466</v>
+      </c>
+      <c r="E121" t="s">
         <v>81</v>
       </c>
-      <c r="C121" t="s">
-        <v>52</v>
-      </c>
-      <c r="D121">
-        <v>447</v>
-      </c>
-      <c r="E121" t="s">
-        <v>53</v>
-      </c>
       <c r="F121" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G121" t="s">
         <v>19</v>
@@ -3785,13 +3769,13 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C122" t="s">
         <v>52</v>
       </c>
       <c r="D122">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E122" t="s">
         <v>82</v>
@@ -3808,53 +3792,53 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C123" t="s">
         <v>52</v>
       </c>
       <c r="D123">
-        <v>470</v>
+        <v>27</v>
       </c>
       <c r="E123" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F123" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G123" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
+        <v>83</v>
+      </c>
+      <c r="C124" t="s">
+        <v>52</v>
+      </c>
+      <c r="D124">
+        <v>42</v>
+      </c>
+      <c r="E124" t="s">
         <v>84</v>
       </c>
-      <c r="C124" t="s">
-        <v>52</v>
-      </c>
-      <c r="D124">
-        <v>27</v>
-      </c>
-      <c r="E124" t="s">
-        <v>80</v>
-      </c>
       <c r="F124" t="s">
         <v>11</v>
       </c>
       <c r="G124" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C125" t="s">
         <v>52</v>
@@ -3863,13 +3847,13 @@
         <v>42</v>
       </c>
       <c r="E125" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F125" t="s">
         <v>11</v>
       </c>
       <c r="G125" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
@@ -3877,22 +3861,22 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C126" t="s">
         <v>52</v>
       </c>
       <c r="D126">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="E126" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F126" t="s">
         <v>11</v>
       </c>
       <c r="G126" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
@@ -3900,16 +3884,16 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C127" t="s">
         <v>52</v>
       </c>
       <c r="D127">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E127" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F127" t="s">
         <v>11</v>
@@ -3923,16 +3907,16 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C128" t="s">
         <v>52</v>
       </c>
       <c r="D128">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E128" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F128" t="s">
         <v>11</v>
@@ -3943,25 +3927,25 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B129" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C129" t="s">
         <v>52</v>
       </c>
       <c r="D129">
-        <v>125</v>
+        <v>515</v>
       </c>
       <c r="E129" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F129" t="s">
         <v>11</v>
       </c>
       <c r="G129" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
@@ -3969,13 +3953,13 @@
         <v>33</v>
       </c>
       <c r="B130" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C130" t="s">
         <v>52</v>
       </c>
       <c r="D130">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E130" t="s">
         <v>50</v>
@@ -3998,10 +3982,10 @@
         <v>52</v>
       </c>
       <c r="D131">
-        <v>516</v>
+        <v>6</v>
       </c>
       <c r="E131" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="F131" t="s">
         <v>11</v>
@@ -4015,16 +3999,16 @@
         <v>33</v>
       </c>
       <c r="B132" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C132" t="s">
         <v>52</v>
       </c>
       <c r="D132">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F132" t="s">
         <v>11</v>
@@ -4038,7 +4022,7 @@
         <v>33</v>
       </c>
       <c r="B133" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C133" t="s">
         <v>52</v>
@@ -4061,16 +4045,16 @@
         <v>33</v>
       </c>
       <c r="B134" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C134" t="s">
         <v>52</v>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F134" t="s">
         <v>11</v>
@@ -4084,16 +4068,16 @@
         <v>33</v>
       </c>
       <c r="B135" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C135" t="s">
         <v>52</v>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="E135" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -4107,13 +4091,13 @@
         <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C136" t="s">
         <v>52</v>
       </c>
       <c r="D136">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E136" t="s">
         <v>50</v>
@@ -4130,13 +4114,13 @@
         <v>33</v>
       </c>
       <c r="B137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C137" t="s">
         <v>52</v>
       </c>
       <c r="D137">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="E137" t="s">
         <v>50</v>
@@ -4153,13 +4137,13 @@
         <v>33</v>
       </c>
       <c r="B138" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C138" t="s">
         <v>52</v>
       </c>
       <c r="D138">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E138" t="s">
         <v>50</v>
@@ -4182,10 +4166,10 @@
         <v>52</v>
       </c>
       <c r="D139">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="E139" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F139" t="s">
         <v>11</v>
@@ -4199,16 +4183,16 @@
         <v>33</v>
       </c>
       <c r="B140" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C140" t="s">
         <v>52</v>
       </c>
       <c r="D140">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E140" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F140" t="s">
         <v>11</v>
@@ -4222,13 +4206,13 @@
         <v>33</v>
       </c>
       <c r="B141" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C141" t="s">
         <v>52</v>
       </c>
       <c r="D141">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E141" t="s">
         <v>50</v>
@@ -4245,13 +4229,13 @@
         <v>33</v>
       </c>
       <c r="B142" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C142" t="s">
         <v>52</v>
       </c>
       <c r="D142">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E142" t="s">
         <v>50</v>
@@ -4268,13 +4252,13 @@
         <v>33</v>
       </c>
       <c r="B143" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C143" t="s">
         <v>52</v>
       </c>
       <c r="D143">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E143" t="s">
         <v>50</v>
@@ -4291,16 +4275,16 @@
         <v>33</v>
       </c>
       <c r="B144" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C144" t="s">
         <v>52</v>
       </c>
       <c r="D144">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="E144" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F144" t="s">
         <v>11</v>
@@ -4311,7 +4295,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B145" t="s">
         <v>97</v>
@@ -4320,39 +4304,39 @@
         <v>52</v>
       </c>
       <c r="D145">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="E145" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F145" t="s">
         <v>11</v>
       </c>
       <c r="G145" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B146" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C146" t="s">
         <v>52</v>
       </c>
       <c r="D146">
-        <v>58</v>
+        <v>220</v>
       </c>
       <c r="E146" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="F146" t="s">
         <v>11</v>
       </c>
       <c r="G146" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
@@ -4360,16 +4344,16 @@
         <v>33</v>
       </c>
       <c r="B147" t="s">
+        <v>97</v>
+      </c>
+      <c r="C147" t="s">
+        <v>52</v>
+      </c>
+      <c r="D147">
+        <v>230</v>
+      </c>
+      <c r="E147" t="s">
         <v>98</v>
-      </c>
-      <c r="C147" t="s">
-        <v>52</v>
-      </c>
-      <c r="D147">
-        <v>220</v>
-      </c>
-      <c r="E147" t="s">
-        <v>54</v>
       </c>
       <c r="F147" t="s">
         <v>11</v>
@@ -4383,16 +4367,16 @@
         <v>33</v>
       </c>
       <c r="B148" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C148" t="s">
         <v>52</v>
       </c>
       <c r="D148">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="E148" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F148" t="s">
         <v>11</v>
@@ -4406,16 +4390,16 @@
         <v>33</v>
       </c>
       <c r="B149" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C149" t="s">
         <v>52</v>
       </c>
       <c r="D149">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="E149" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F149" t="s">
         <v>11</v>
@@ -4429,13 +4413,13 @@
         <v>33</v>
       </c>
       <c r="B150" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C150" t="s">
         <v>52</v>
       </c>
       <c r="D150">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E150" t="s">
         <v>50</v>
@@ -4449,25 +4433,25 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C151" t="s">
         <v>52</v>
       </c>
       <c r="D151">
-        <v>266</v>
+        <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F151" t="s">
         <v>11</v>
       </c>
       <c r="G151" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
@@ -4475,13 +4459,13 @@
         <v>7</v>
       </c>
       <c r="B152" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C152" t="s">
         <v>52</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E152" t="s">
         <v>101</v>
@@ -4490,7 +4474,7 @@
         <v>11</v>
       </c>
       <c r="G152" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
@@ -4498,22 +4482,22 @@
         <v>7</v>
       </c>
       <c r="B153" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C153" t="s">
         <v>52</v>
       </c>
       <c r="D153">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E153" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="F153" t="s">
         <v>11</v>
       </c>
       <c r="G153" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
@@ -4521,13 +4505,13 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C154" t="s">
         <v>52</v>
       </c>
       <c r="D154">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E154" t="s">
         <v>45</v>
@@ -4544,13 +4528,13 @@
         <v>7</v>
       </c>
       <c r="B155" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C155" t="s">
         <v>52</v>
       </c>
       <c r="D155">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E155" t="s">
         <v>45</v>
@@ -4567,22 +4551,22 @@
         <v>7</v>
       </c>
       <c r="B156" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C156" t="s">
         <v>52</v>
       </c>
       <c r="D156">
-        <v>110</v>
+        <v>185</v>
       </c>
       <c r="E156" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F156" t="s">
         <v>11</v>
       </c>
       <c r="G156" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -4590,13 +4574,13 @@
         <v>7</v>
       </c>
       <c r="B157" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C157" t="s">
         <v>52</v>
       </c>
       <c r="D157">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -4613,13 +4597,13 @@
         <v>7</v>
       </c>
       <c r="B158" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C158" t="s">
         <v>52</v>
       </c>
       <c r="D158">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
@@ -4633,42 +4617,42 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B159" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C159" t="s">
         <v>52</v>
       </c>
       <c r="D159">
-        <v>188</v>
+        <v>481</v>
       </c>
       <c r="E159" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="F159" t="s">
         <v>11</v>
       </c>
       <c r="G159" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B160" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C160" t="s">
         <v>52</v>
       </c>
       <c r="D160">
-        <v>405</v>
+        <v>10</v>
       </c>
       <c r="E160" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F160" t="s">
         <v>11</v>
@@ -4682,45 +4666,45 @@
         <v>33</v>
       </c>
       <c r="B161" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C161" t="s">
         <v>52</v>
       </c>
       <c r="D161">
-        <v>481</v>
+        <v>10</v>
       </c>
       <c r="E161" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="F161" t="s">
         <v>11</v>
       </c>
       <c r="G161" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B162" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C162" t="s">
         <v>52</v>
       </c>
       <c r="D162">
-        <v>578</v>
+        <v>25</v>
       </c>
       <c r="E162" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="F162" t="s">
         <v>11</v>
       </c>
       <c r="G162" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
@@ -4728,45 +4712,45 @@
         <v>7</v>
       </c>
       <c r="B163" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C163" t="s">
         <v>52</v>
       </c>
       <c r="D163">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E163" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F163" t="s">
         <v>11</v>
       </c>
       <c r="G163" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B164" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C164" t="s">
         <v>52</v>
       </c>
       <c r="D164">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E164" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="F164" t="s">
         <v>11</v>
       </c>
       <c r="G164" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
@@ -4774,85 +4758,85 @@
         <v>7</v>
       </c>
       <c r="B165" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C165" t="s">
         <v>52</v>
       </c>
       <c r="D165">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E165" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F165" t="s">
         <v>11</v>
       </c>
       <c r="G165" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B166" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C166" t="s">
         <v>52</v>
       </c>
       <c r="D166">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="E166" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F166" t="s">
         <v>11</v>
       </c>
       <c r="G166" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B167" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C167" t="s">
         <v>52</v>
       </c>
       <c r="D167">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="E167" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F167" t="s">
         <v>11</v>
       </c>
       <c r="G167" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B168" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C168" t="s">
         <v>52</v>
       </c>
       <c r="D168">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="E168" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="F168" t="s">
         <v>11</v>
@@ -4866,22 +4850,22 @@
         <v>33</v>
       </c>
       <c r="B169" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C169" t="s">
         <v>52</v>
       </c>
       <c r="D169">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="E169" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="F169" t="s">
         <v>11</v>
       </c>
       <c r="G169" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -4889,16 +4873,16 @@
         <v>33</v>
       </c>
       <c r="B170" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C170" t="s">
         <v>52</v>
       </c>
       <c r="D170">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E170" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F170" t="s">
         <v>11</v>
@@ -4912,16 +4896,16 @@
         <v>33</v>
       </c>
       <c r="B171" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C171" t="s">
         <v>52</v>
       </c>
       <c r="D171">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="E171" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F171" t="s">
         <v>11</v>
@@ -4932,25 +4916,25 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C172" t="s">
         <v>52</v>
       </c>
       <c r="D172">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="E172" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F172" t="s">
         <v>11</v>
       </c>
       <c r="G172" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
@@ -4958,16 +4942,16 @@
         <v>33</v>
       </c>
       <c r="B173" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C173" t="s">
         <v>52</v>
       </c>
       <c r="D173">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="E173" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="F173" t="s">
         <v>11</v>
@@ -4978,25 +4962,25 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B174" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C174" t="s">
         <v>52</v>
       </c>
       <c r="D174">
-        <v>245</v>
+        <v>386</v>
       </c>
       <c r="E174" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F174" t="s">
         <v>11</v>
       </c>
       <c r="G174" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
@@ -5004,45 +4988,45 @@
         <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C175" t="s">
         <v>52</v>
       </c>
       <c r="D175">
-        <v>256</v>
+        <v>60</v>
       </c>
       <c r="E175" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="F175" t="s">
         <v>11</v>
       </c>
       <c r="G175" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C176" t="s">
         <v>52</v>
       </c>
       <c r="D176">
-        <v>266</v>
+        <v>61</v>
       </c>
       <c r="E176" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="F176" t="s">
         <v>11</v>
       </c>
       <c r="G176" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
@@ -5050,22 +5034,22 @@
         <v>7</v>
       </c>
       <c r="B177" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C177" t="s">
         <v>52</v>
       </c>
       <c r="D177">
-        <v>386</v>
+        <v>62</v>
       </c>
       <c r="E177" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F177" t="s">
         <v>11</v>
       </c>
       <c r="G177" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
@@ -5073,22 +5057,22 @@
         <v>7</v>
       </c>
       <c r="B178" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C178" t="s">
         <v>52</v>
       </c>
       <c r="D178">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="E178" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="F178" t="s">
         <v>11</v>
       </c>
       <c r="G178" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
@@ -5096,22 +5080,22 @@
         <v>7</v>
       </c>
       <c r="B179" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C179" t="s">
         <v>52</v>
       </c>
       <c r="D179">
-        <v>61</v>
+        <v>162</v>
       </c>
       <c r="E179" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="F179" t="s">
         <v>11</v>
       </c>
       <c r="G179" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
@@ -5119,91 +5103,91 @@
         <v>7</v>
       </c>
       <c r="B180" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C180" t="s">
         <v>52</v>
       </c>
       <c r="D180">
-        <v>62</v>
+        <v>164</v>
       </c>
       <c r="E180" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="F180" t="s">
         <v>11</v>
       </c>
       <c r="G180" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B181" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C181" t="s">
         <v>52</v>
       </c>
       <c r="D181">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="E181" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F181" t="s">
         <v>11</v>
       </c>
       <c r="G181" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B182" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C182" t="s">
         <v>52</v>
       </c>
       <c r="D182">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="E182" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F182" t="s">
         <v>11</v>
       </c>
       <c r="G182" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B183" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C183" t="s">
         <v>52</v>
       </c>
       <c r="D183">
-        <v>164</v>
+        <v>437</v>
       </c>
       <c r="E183" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="F183" t="s">
         <v>11</v>
       </c>
       <c r="G183" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -5217,10 +5201,10 @@
         <v>52</v>
       </c>
       <c r="D184">
-        <v>199</v>
+        <v>468</v>
       </c>
       <c r="E184" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="F184" t="s">
         <v>11</v>
@@ -5234,13 +5218,13 @@
         <v>33</v>
       </c>
       <c r="B185" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C185" t="s">
         <v>52</v>
       </c>
       <c r="D185">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="E185" t="s">
         <v>54</v>
@@ -5257,16 +5241,16 @@
         <v>33</v>
       </c>
       <c r="B186" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C186" t="s">
         <v>52</v>
       </c>
       <c r="D186">
-        <v>361</v>
+        <v>209</v>
       </c>
       <c r="E186" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="F186" t="s">
         <v>11</v>
@@ -5280,16 +5264,16 @@
         <v>33</v>
       </c>
       <c r="B187" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C187" t="s">
         <v>52</v>
       </c>
       <c r="D187">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="E187" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="F187" t="s">
         <v>11</v>
@@ -5303,16 +5287,16 @@
         <v>33</v>
       </c>
       <c r="B188" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C188" t="s">
         <v>52</v>
       </c>
       <c r="D188">
-        <v>534</v>
+        <v>30</v>
       </c>
       <c r="E188" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="F188" t="s">
         <v>11</v>
@@ -5326,16 +5310,16 @@
         <v>33</v>
       </c>
       <c r="B189" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C189" t="s">
         <v>52</v>
       </c>
       <c r="D189">
-        <v>468</v>
+        <v>44</v>
       </c>
       <c r="E189" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="F189" t="s">
         <v>11</v>
@@ -5349,16 +5333,16 @@
         <v>33</v>
       </c>
       <c r="B190" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C190" t="s">
         <v>52</v>
       </c>
       <c r="D190">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E190" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="F190" t="s">
         <v>11</v>
@@ -5372,16 +5356,16 @@
         <v>33</v>
       </c>
       <c r="B191" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C191" t="s">
         <v>52</v>
       </c>
       <c r="D191">
-        <v>209</v>
+        <v>97</v>
       </c>
       <c r="E191" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="F191" t="s">
         <v>11</v>
@@ -5392,19 +5376,19 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B192" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C192" t="s">
         <v>52</v>
       </c>
       <c r="D192">
-        <v>209</v>
+        <v>10</v>
       </c>
       <c r="E192" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="F192" t="s">
         <v>11</v>
@@ -5418,22 +5402,22 @@
         <v>33</v>
       </c>
       <c r="B193" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C193" t="s">
         <v>52</v>
       </c>
       <c r="D193">
-        <v>450</v>
+        <v>55</v>
       </c>
       <c r="E193" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F193" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G193" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
@@ -5441,22 +5425,22 @@
         <v>33</v>
       </c>
       <c r="B194" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C194" t="s">
         <v>52</v>
       </c>
       <c r="D194">
-        <v>30</v>
+        <v>776</v>
       </c>
       <c r="E194" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F194" t="s">
         <v>11</v>
       </c>
       <c r="G194" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
@@ -5464,22 +5448,22 @@
         <v>33</v>
       </c>
       <c r="B195" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C195" t="s">
         <v>52</v>
       </c>
       <c r="D195">
-        <v>44</v>
+        <v>844</v>
       </c>
       <c r="E195" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F195" t="s">
         <v>11</v>
       </c>
       <c r="G195" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
@@ -5487,22 +5471,22 @@
         <v>33</v>
       </c>
       <c r="B196" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C196" t="s">
         <v>52</v>
       </c>
       <c r="D196">
-        <v>20</v>
+        <v>873</v>
       </c>
       <c r="E196" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="F196" t="s">
         <v>11</v>
       </c>
       <c r="G196" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
@@ -5510,27 +5494,27 @@
         <v>33</v>
       </c>
       <c r="B197" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C197" t="s">
         <v>52</v>
       </c>
       <c r="D197">
-        <v>97</v>
+        <v>878</v>
       </c>
       <c r="E197" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F197" t="s">
         <v>11</v>
       </c>
       <c r="G197" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B198" t="s">
         <v>119</v>
@@ -5539,16 +5523,16 @@
         <v>52</v>
       </c>
       <c r="D198">
-        <v>10</v>
+        <v>894</v>
       </c>
       <c r="E198" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="F198" t="s">
         <v>11</v>
       </c>
       <c r="G198" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
@@ -5562,16 +5546,16 @@
         <v>52</v>
       </c>
       <c r="D199">
-        <v>55</v>
+        <v>1008</v>
       </c>
       <c r="E199" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F199" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G199" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
@@ -5579,22 +5563,22 @@
         <v>33</v>
       </c>
       <c r="B200" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C200" t="s">
         <v>52</v>
       </c>
       <c r="D200">
-        <v>776</v>
+        <v>1113</v>
       </c>
       <c r="E200" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F200" t="s">
         <v>11</v>
       </c>
       <c r="G200" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
@@ -5602,22 +5586,22 @@
         <v>33</v>
       </c>
       <c r="B201" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C201" t="s">
         <v>52</v>
       </c>
       <c r="D201">
-        <v>844</v>
+        <v>1117</v>
       </c>
       <c r="E201" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F201" t="s">
         <v>11</v>
       </c>
       <c r="G201" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
@@ -5625,22 +5609,22 @@
         <v>33</v>
       </c>
       <c r="B202" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C202" t="s">
         <v>52</v>
       </c>
       <c r="D202">
-        <v>873</v>
+        <v>1148</v>
       </c>
       <c r="E202" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F202" t="s">
         <v>11</v>
       </c>
       <c r="G202" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
@@ -5648,22 +5632,22 @@
         <v>33</v>
       </c>
       <c r="B203" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C203" t="s">
         <v>52</v>
       </c>
       <c r="D203">
-        <v>878</v>
+        <v>1520</v>
       </c>
       <c r="E203" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F203" t="s">
         <v>11</v>
       </c>
       <c r="G203" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
@@ -5671,22 +5655,22 @@
         <v>33</v>
       </c>
       <c r="B204" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C204" t="s">
         <v>52</v>
       </c>
       <c r="D204">
-        <v>894</v>
+        <v>1526</v>
       </c>
       <c r="E204" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F204" t="s">
         <v>11</v>
       </c>
       <c r="G204" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
@@ -5694,22 +5678,22 @@
         <v>33</v>
       </c>
       <c r="B205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C205" t="s">
         <v>52</v>
       </c>
       <c r="D205">
-        <v>1008</v>
+        <v>1785</v>
       </c>
       <c r="E205" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F205" t="s">
         <v>11</v>
       </c>
       <c r="G205" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
@@ -5717,22 +5701,22 @@
         <v>33</v>
       </c>
       <c r="B206" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C206" t="s">
         <v>52</v>
       </c>
       <c r="D206">
-        <v>1113</v>
+        <v>2053</v>
       </c>
       <c r="E206" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F206" t="s">
         <v>11</v>
       </c>
       <c r="G206" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
@@ -5740,22 +5724,22 @@
         <v>33</v>
       </c>
       <c r="B207" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C207" t="s">
         <v>52</v>
       </c>
       <c r="D207">
-        <v>1117</v>
+        <v>2293</v>
       </c>
       <c r="E207" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F207" t="s">
         <v>11</v>
       </c>
       <c r="G207" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
@@ -5763,22 +5747,22 @@
         <v>33</v>
       </c>
       <c r="B208" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C208" t="s">
         <v>52</v>
       </c>
       <c r="D208">
-        <v>1148</v>
+        <v>2300</v>
       </c>
       <c r="E208" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F208" t="s">
         <v>11</v>
       </c>
       <c r="G208" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
@@ -5786,22 +5770,22 @@
         <v>33</v>
       </c>
       <c r="B209" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C209" t="s">
         <v>52</v>
       </c>
       <c r="D209">
-        <v>1520</v>
+        <v>2809</v>
       </c>
       <c r="E209" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F209" t="s">
         <v>11</v>
       </c>
       <c r="G209" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
@@ -5809,22 +5793,22 @@
         <v>33</v>
       </c>
       <c r="B210" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C210" t="s">
         <v>52</v>
       </c>
       <c r="D210">
-        <v>1526</v>
+        <v>2915</v>
       </c>
       <c r="E210" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F210" t="s">
         <v>11</v>
       </c>
       <c r="G210" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
@@ -5832,22 +5816,22 @@
         <v>33</v>
       </c>
       <c r="B211" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C211" t="s">
         <v>52</v>
       </c>
       <c r="D211">
-        <v>1785</v>
+        <v>2928</v>
       </c>
       <c r="E211" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F211" t="s">
         <v>11</v>
       </c>
       <c r="G211" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
@@ -5855,22 +5839,22 @@
         <v>33</v>
       </c>
       <c r="B212" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C212" t="s">
         <v>52</v>
       </c>
       <c r="D212">
-        <v>2053</v>
+        <v>2934</v>
       </c>
       <c r="E212" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F212" t="s">
         <v>11</v>
       </c>
       <c r="G212" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
@@ -5878,22 +5862,22 @@
         <v>33</v>
       </c>
       <c r="B213" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C213" t="s">
         <v>52</v>
       </c>
       <c r="D213">
-        <v>2293</v>
+        <v>3084</v>
       </c>
       <c r="E213" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F213" t="s">
         <v>11</v>
       </c>
       <c r="G213" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
@@ -5901,22 +5885,22 @@
         <v>33</v>
       </c>
       <c r="B214" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C214" t="s">
         <v>52</v>
       </c>
       <c r="D214">
-        <v>2300</v>
+        <v>3328</v>
       </c>
       <c r="E214" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F214" t="s">
         <v>11</v>
       </c>
       <c r="G214" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
@@ -5924,22 +5908,22 @@
         <v>33</v>
       </c>
       <c r="B215" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C215" t="s">
         <v>52</v>
       </c>
       <c r="D215">
-        <v>2809</v>
+        <v>3353</v>
       </c>
       <c r="E215" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F215" t="s">
         <v>11</v>
       </c>
       <c r="G215" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -5947,22 +5931,22 @@
         <v>33</v>
       </c>
       <c r="B216" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C216" t="s">
         <v>52</v>
       </c>
       <c r="D216">
-        <v>2915</v>
+        <v>3477</v>
       </c>
       <c r="E216" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F216" t="s">
         <v>11</v>
       </c>
       <c r="G216" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
@@ -5970,22 +5954,22 @@
         <v>33</v>
       </c>
       <c r="B217" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C217" t="s">
         <v>52</v>
       </c>
       <c r="D217">
-        <v>2928</v>
+        <v>3504</v>
       </c>
       <c r="E217" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F217" t="s">
         <v>11</v>
       </c>
       <c r="G217" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
@@ -5993,22 +5977,22 @@
         <v>33</v>
       </c>
       <c r="B218" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C218" t="s">
         <v>52</v>
       </c>
       <c r="D218">
-        <v>2934</v>
+        <v>3514</v>
       </c>
       <c r="E218" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F218" t="s">
         <v>11</v>
       </c>
       <c r="G218" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
@@ -6016,22 +6000,22 @@
         <v>33</v>
       </c>
       <c r="B219" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C219" t="s">
         <v>52</v>
       </c>
       <c r="D219">
-        <v>3084</v>
+        <v>3539</v>
       </c>
       <c r="E219" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F219" t="s">
         <v>11</v>
       </c>
       <c r="G219" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
@@ -6039,22 +6023,22 @@
         <v>33</v>
       </c>
       <c r="B220" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C220" t="s">
         <v>52</v>
       </c>
       <c r="D220">
-        <v>3328</v>
+        <v>3548</v>
       </c>
       <c r="E220" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F220" t="s">
         <v>11</v>
       </c>
       <c r="G220" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
@@ -6062,22 +6046,22 @@
         <v>33</v>
       </c>
       <c r="B221" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C221" t="s">
         <v>52</v>
       </c>
       <c r="D221">
-        <v>3353</v>
+        <v>3558</v>
       </c>
       <c r="E221" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F221" t="s">
         <v>11</v>
       </c>
       <c r="G221" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -6085,22 +6069,22 @@
         <v>33</v>
       </c>
       <c r="B222" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C222" t="s">
         <v>52</v>
       </c>
       <c r="D222">
-        <v>3477</v>
+        <v>3614</v>
       </c>
       <c r="E222" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F222" t="s">
         <v>11</v>
       </c>
       <c r="G222" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
@@ -6108,22 +6092,22 @@
         <v>33</v>
       </c>
       <c r="B223" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C223" t="s">
         <v>52</v>
       </c>
       <c r="D223">
-        <v>3504</v>
+        <v>3620</v>
       </c>
       <c r="E223" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F223" t="s">
         <v>11</v>
       </c>
       <c r="G223" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
@@ -6131,22 +6115,22 @@
         <v>33</v>
       </c>
       <c r="B224" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C224" t="s">
         <v>52</v>
       </c>
       <c r="D224">
-        <v>3514</v>
+        <v>3624</v>
       </c>
       <c r="E224" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F224" t="s">
         <v>11</v>
       </c>
       <c r="G224" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -6154,22 +6138,22 @@
         <v>33</v>
       </c>
       <c r="B225" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C225" t="s">
         <v>52</v>
       </c>
       <c r="D225">
-        <v>3539</v>
+        <v>3629</v>
       </c>
       <c r="E225" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F225" t="s">
         <v>11</v>
       </c>
       <c r="G225" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
@@ -6177,22 +6161,22 @@
         <v>33</v>
       </c>
       <c r="B226" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C226" t="s">
         <v>52</v>
       </c>
       <c r="D226">
-        <v>3548</v>
+        <v>3664</v>
       </c>
       <c r="E226" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F226" t="s">
         <v>11</v>
       </c>
       <c r="G226" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
@@ -6200,22 +6184,22 @@
         <v>33</v>
       </c>
       <c r="B227" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C227" t="s">
         <v>52</v>
       </c>
       <c r="D227">
-        <v>3558</v>
+        <v>3931</v>
       </c>
       <c r="E227" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F227" t="s">
         <v>11</v>
       </c>
       <c r="G227" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -6223,22 +6207,22 @@
         <v>33</v>
       </c>
       <c r="B228" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C228" t="s">
         <v>52</v>
       </c>
       <c r="D228">
-        <v>3614</v>
+        <v>3941</v>
       </c>
       <c r="E228" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F228" t="s">
         <v>11</v>
       </c>
       <c r="G228" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
@@ -6246,22 +6230,22 @@
         <v>33</v>
       </c>
       <c r="B229" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C229" t="s">
         <v>52</v>
       </c>
       <c r="D229">
-        <v>3620</v>
+        <v>3946</v>
       </c>
       <c r="E229" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F229" t="s">
         <v>11</v>
       </c>
       <c r="G229" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
@@ -6269,22 +6253,22 @@
         <v>33</v>
       </c>
       <c r="B230" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C230" t="s">
         <v>52</v>
       </c>
       <c r="D230">
-        <v>3624</v>
+        <v>3959</v>
       </c>
       <c r="E230" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F230" t="s">
         <v>11</v>
       </c>
       <c r="G230" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
@@ -6292,22 +6276,22 @@
         <v>33</v>
       </c>
       <c r="B231" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C231" t="s">
         <v>52</v>
       </c>
       <c r="D231">
-        <v>3629</v>
+        <v>3967</v>
       </c>
       <c r="E231" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F231" t="s">
         <v>11</v>
       </c>
       <c r="G231" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
@@ -6315,22 +6299,22 @@
         <v>33</v>
       </c>
       <c r="B232" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C232" t="s">
         <v>52</v>
       </c>
       <c r="D232">
-        <v>3664</v>
+        <v>4033</v>
       </c>
       <c r="E232" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F232" t="s">
         <v>11</v>
       </c>
       <c r="G232" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
@@ -6338,22 +6322,22 @@
         <v>33</v>
       </c>
       <c r="B233" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C233" t="s">
         <v>52</v>
       </c>
       <c r="D233">
-        <v>3931</v>
+        <v>4227</v>
       </c>
       <c r="E233" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="F233" t="s">
         <v>11</v>
       </c>
       <c r="G233" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
@@ -6361,22 +6345,22 @@
         <v>33</v>
       </c>
       <c r="B234" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C234" t="s">
         <v>52</v>
       </c>
       <c r="D234">
-        <v>3941</v>
+        <v>4234</v>
       </c>
       <c r="E234" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F234" t="s">
         <v>11</v>
       </c>
       <c r="G234" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
@@ -6384,22 +6368,22 @@
         <v>33</v>
       </c>
       <c r="B235" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C235" t="s">
         <v>52</v>
       </c>
       <c r="D235">
-        <v>3946</v>
+        <v>4418</v>
       </c>
       <c r="E235" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F235" t="s">
         <v>11</v>
       </c>
       <c r="G235" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
@@ -6407,22 +6391,22 @@
         <v>33</v>
       </c>
       <c r="B236" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C236" t="s">
         <v>52</v>
       </c>
       <c r="D236">
-        <v>3959</v>
+        <v>4436</v>
       </c>
       <c r="E236" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F236" t="s">
         <v>11</v>
       </c>
       <c r="G236" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
@@ -6430,22 +6414,22 @@
         <v>33</v>
       </c>
       <c r="B237" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C237" t="s">
         <v>52</v>
       </c>
       <c r="D237">
-        <v>3967</v>
+        <v>4490</v>
       </c>
       <c r="E237" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F237" t="s">
         <v>11</v>
       </c>
       <c r="G237" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -6453,22 +6437,22 @@
         <v>33</v>
       </c>
       <c r="B238" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C238" t="s">
         <v>52</v>
       </c>
       <c r="D238">
-        <v>4033</v>
+        <v>4497</v>
       </c>
       <c r="E238" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="F238" t="s">
         <v>11</v>
       </c>
       <c r="G238" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -6476,22 +6460,22 @@
         <v>33</v>
       </c>
       <c r="B239" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C239" t="s">
         <v>52</v>
       </c>
       <c r="D239">
-        <v>4227</v>
+        <v>4501</v>
       </c>
       <c r="E239" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="F239" t="s">
         <v>11</v>
       </c>
       <c r="G239" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
@@ -6499,22 +6483,22 @@
         <v>33</v>
       </c>
       <c r="B240" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C240" t="s">
         <v>52</v>
       </c>
       <c r="D240">
-        <v>4234</v>
+        <v>4508</v>
       </c>
       <c r="E240" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F240" t="s">
         <v>11</v>
       </c>
       <c r="G240" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
@@ -6522,22 +6506,22 @@
         <v>33</v>
       </c>
       <c r="B241" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C241" t="s">
         <v>52</v>
       </c>
       <c r="D241">
-        <v>4418</v>
+        <v>4519</v>
       </c>
       <c r="E241" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F241" t="s">
         <v>11</v>
       </c>
       <c r="G241" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
@@ -6545,22 +6529,22 @@
         <v>33</v>
       </c>
       <c r="B242" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C242" t="s">
         <v>52</v>
       </c>
       <c r="D242">
-        <v>4436</v>
+        <v>4527</v>
       </c>
       <c r="E242" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F242" t="s">
         <v>11</v>
       </c>
       <c r="G242" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
@@ -6568,22 +6552,22 @@
         <v>33</v>
       </c>
       <c r="B243" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C243" t="s">
         <v>52</v>
       </c>
       <c r="D243">
-        <v>4490</v>
+        <v>4533</v>
       </c>
       <c r="E243" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F243" t="s">
         <v>11</v>
       </c>
       <c r="G243" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
@@ -6591,22 +6575,22 @@
         <v>33</v>
       </c>
       <c r="B244" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C244" t="s">
         <v>52</v>
       </c>
       <c r="D244">
-        <v>4497</v>
+        <v>4585</v>
       </c>
       <c r="E244" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="F244" t="s">
         <v>11</v>
       </c>
       <c r="G244" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
@@ -6614,22 +6598,22 @@
         <v>33</v>
       </c>
       <c r="B245" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C245" t="s">
         <v>52</v>
       </c>
       <c r="D245">
-        <v>4501</v>
+        <v>4627</v>
       </c>
       <c r="E245" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F245" t="s">
         <v>11</v>
       </c>
       <c r="G245" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
@@ -6637,22 +6621,22 @@
         <v>33</v>
       </c>
       <c r="B246" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C246" t="s">
         <v>52</v>
       </c>
       <c r="D246">
-        <v>4508</v>
+        <v>4635</v>
       </c>
       <c r="E246" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="F246" t="s">
         <v>11</v>
       </c>
       <c r="G246" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
@@ -6660,22 +6644,22 @@
         <v>33</v>
       </c>
       <c r="B247" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C247" t="s">
         <v>52</v>
       </c>
       <c r="D247">
-        <v>4519</v>
+        <v>4640</v>
       </c>
       <c r="E247" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F247" t="s">
         <v>11</v>
       </c>
       <c r="G247" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
@@ -6683,22 +6667,22 @@
         <v>33</v>
       </c>
       <c r="B248" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C248" t="s">
         <v>52</v>
       </c>
       <c r="D248">
-        <v>4527</v>
+        <v>4647</v>
       </c>
       <c r="E248" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F248" t="s">
         <v>11</v>
       </c>
       <c r="G248" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
@@ -6706,256 +6690,119 @@
         <v>33</v>
       </c>
       <c r="B249" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C249" t="s">
         <v>52</v>
       </c>
       <c r="D249">
-        <v>4533</v>
+        <v>4689</v>
       </c>
       <c r="E249" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F249" t="s">
         <v>11</v>
       </c>
       <c r="G249" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B250" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="C250" t="s">
         <v>52</v>
       </c>
       <c r="D250">
-        <v>4585</v>
+        <v>40</v>
       </c>
       <c r="E250" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="F250" t="s">
         <v>11</v>
       </c>
       <c r="G250" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B251" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="C251" t="s">
         <v>52</v>
       </c>
       <c r="D251">
-        <v>4627</v>
+        <v>80</v>
       </c>
       <c r="E251" t="s">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="F251" t="s">
         <v>11</v>
       </c>
       <c r="G251" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B252" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C252" t="s">
         <v>52</v>
       </c>
       <c r="D252">
-        <v>4635</v>
+        <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="F252" t="s">
         <v>11</v>
       </c>
       <c r="G252" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A253" t="s">
-        <v>33</v>
-      </c>
-      <c r="B253" t="s">
-        <v>122</v>
-      </c>
-      <c r="C253" t="s">
-        <v>52</v>
-      </c>
-      <c r="D253">
-        <v>4640</v>
-      </c>
-      <c r="E253" t="s">
-        <v>166</v>
-      </c>
-      <c r="F253" t="s">
-        <v>11</v>
-      </c>
-      <c r="G253" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
-        <v>33</v>
-      </c>
-      <c r="B254" t="s">
-        <v>122</v>
-      </c>
-      <c r="C254" t="s">
-        <v>52</v>
-      </c>
-      <c r="D254">
-        <v>4647</v>
-      </c>
-      <c r="E254" t="s">
-        <v>167</v>
-      </c>
-      <c r="F254" t="s">
-        <v>11</v>
-      </c>
-      <c r="G254" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
-        <v>33</v>
-      </c>
-      <c r="B255" t="s">
-        <v>122</v>
-      </c>
-      <c r="C255" t="s">
-        <v>52</v>
-      </c>
-      <c r="D255">
-        <v>4689</v>
-      </c>
-      <c r="E255" t="s">
-        <v>168</v>
-      </c>
-      <c r="F255" t="s">
-        <v>11</v>
-      </c>
-      <c r="G255" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
-        <v>7</v>
-      </c>
-      <c r="B256" t="s">
-        <v>169</v>
-      </c>
-      <c r="C256" t="s">
-        <v>52</v>
-      </c>
-      <c r="D256">
-        <v>40</v>
-      </c>
-      <c r="E256" t="s">
-        <v>21</v>
-      </c>
-      <c r="F256" t="s">
-        <v>11</v>
-      </c>
-      <c r="G256" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A257" t="s">
-        <v>7</v>
-      </c>
-      <c r="B257" t="s">
-        <v>169</v>
-      </c>
-      <c r="C257" t="s">
-        <v>52</v>
-      </c>
-      <c r="D257">
-        <v>80</v>
-      </c>
-      <c r="E257" t="s">
-        <v>42</v>
-      </c>
-      <c r="F257" t="s">
-        <v>11</v>
-      </c>
-      <c r="G257" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A258" t="s">
-        <v>7</v>
-      </c>
-      <c r="B258" t="s">
-        <v>170</v>
-      </c>
-      <c r="C258" t="s">
-        <v>52</v>
-      </c>
-      <c r="D258">
-        <v>2</v>
-      </c>
-      <c r="E258" t="s">
-        <v>171</v>
-      </c>
-      <c r="F258" t="s">
-        <v>11</v>
-      </c>
-      <c r="G258" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="84.7265625" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" customWidth="1"/>
+    <col min="1" max="1" width="62.7265625" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>173</v>
+      <c r="A1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B2">
         <v>56</v>
@@ -6963,15 +6810,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B3">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>187</v>
+      <c r="A4" t="s">
+        <v>173</v>
       </c>
       <c r="B4">
         <v>30</v>
@@ -6987,7 +6834,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B6">
         <v>19</v>
@@ -6995,7 +6842,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7">
         <v>10</v>
@@ -7003,7 +6850,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -7011,7 +6858,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -7019,7 +6866,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -7043,23 +6890,23 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -7067,15 +6914,15 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -7083,23 +6930,23 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="5">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -7107,7 +6954,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -7115,15 +6962,15 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>22</v>
+      <c r="A23" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -7139,7 +6986,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -7155,7 +7002,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -7163,7 +7010,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -7171,7 +7018,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -7187,7 +7034,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -7195,28 +7042,20 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>113</v>
-      </c>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B34">
-        <f>SUM(B2:B33)</f>
-        <v>257</v>
+        <f>SUM(B2:B32)</f>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>